--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117766236</v>
+        <v>117766234</v>
       </c>
       <c r="B2" t="n">
         <v>79561</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755630</v>
+        <v>755615</v>
       </c>
       <c r="R2" t="n">
-        <v>7325593</v>
+        <v>7325527</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766234</v>
+        <v>117766240</v>
       </c>
       <c r="B4" t="n">
         <v>79561</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755615</v>
+        <v>755703</v>
       </c>
       <c r="R4" t="n">
-        <v>7325527</v>
+        <v>7325559</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117766238</v>
+        <v>117766236</v>
       </c>
       <c r="B5" t="n">
         <v>79561</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755637</v>
+        <v>755630</v>
       </c>
       <c r="R5" t="n">
-        <v>7325601</v>
+        <v>7325593</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117766240</v>
+        <v>117766238</v>
       </c>
       <c r="B6" t="n">
         <v>79561</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755703</v>
+        <v>755637</v>
       </c>
       <c r="R6" t="n">
-        <v>7325559</v>
+        <v>7325601</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117766234</v>
+        <v>117766236</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755615</v>
+        <v>755630</v>
       </c>
       <c r="R2" t="n">
-        <v>7325527</v>
+        <v>7325593</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117766232</v>
+        <v>117766234</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755782</v>
+        <v>755615</v>
       </c>
       <c r="R3" t="n">
-        <v>7325338</v>
+        <v>7325527</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766240</v>
+        <v>117766232</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755703</v>
+        <v>755782</v>
       </c>
       <c r="R4" t="n">
-        <v>7325559</v>
+        <v>7325338</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117766236</v>
+        <v>117766238</v>
       </c>
       <c r="B5" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755630</v>
+        <v>755637</v>
       </c>
       <c r="R5" t="n">
-        <v>7325593</v>
+        <v>7325601</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117766238</v>
+        <v>117766240</v>
       </c>
       <c r="B6" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755637</v>
+        <v>755703</v>
       </c>
       <c r="R6" t="n">
-        <v>7325601</v>
+        <v>7325559</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117766228</v>
+        <v>117766230</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>756198</v>
+        <v>756111</v>
       </c>
       <c r="R7" t="n">
-        <v>7324833</v>
+        <v>7325122</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117766230</v>
+        <v>117766228</v>
       </c>
       <c r="B8" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>756111</v>
+        <v>756198</v>
       </c>
       <c r="R8" t="n">
-        <v>7325122</v>
+        <v>7324833</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676892</v>
+        <v>118676881</v>
       </c>
       <c r="B7" t="n">
         <v>79565</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755563</v>
+        <v>755600</v>
       </c>
       <c r="R7" t="n">
-        <v>7325580</v>
+        <v>7325380</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676890</v>
+        <v>118676886</v>
       </c>
       <c r="B8" t="n">
         <v>79565</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755578</v>
+        <v>755563</v>
       </c>
       <c r="R8" t="n">
-        <v>7325600</v>
+        <v>7325460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118676880</v>
+        <v>118676890</v>
       </c>
       <c r="B9" t="n">
         <v>79565</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755615</v>
+        <v>755578</v>
       </c>
       <c r="R9" t="n">
-        <v>7325360</v>
+        <v>7325600</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118676887</v>
+        <v>118676892</v>
       </c>
       <c r="B10" t="n">
         <v>79565</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755550</v>
+        <v>755563</v>
       </c>
       <c r="R10" t="n">
-        <v>7325440</v>
+        <v>7325580</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118676889</v>
+        <v>118676879</v>
       </c>
       <c r="B11" t="n">
         <v>79565</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755541</v>
+        <v>755623</v>
       </c>
       <c r="R11" t="n">
-        <v>7325470</v>
+        <v>7325370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118676893</v>
+        <v>118676889</v>
       </c>
       <c r="B12" t="n">
         <v>79565</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755580</v>
+        <v>755541</v>
       </c>
       <c r="R12" t="n">
-        <v>7325530</v>
+        <v>7325470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118676883</v>
+        <v>118676882</v>
       </c>
       <c r="B13" t="n">
         <v>79565</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755566</v>
+        <v>755529</v>
       </c>
       <c r="R13" t="n">
-        <v>7325430</v>
+        <v>7325440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118676886</v>
+        <v>118676884</v>
       </c>
       <c r="B14" t="n">
         <v>79565</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755563</v>
+        <v>755578</v>
       </c>
       <c r="R14" t="n">
-        <v>7325460</v>
+        <v>7325440</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118676891</v>
+        <v>118676875</v>
       </c>
       <c r="B15" t="n">
         <v>79565</v>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755576</v>
+        <v>755740</v>
       </c>
       <c r="R15" t="n">
-        <v>7325600</v>
+        <v>7325550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118676874</v>
+        <v>118676893</v>
       </c>
       <c r="B16" t="n">
         <v>79565</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755750</v>
+        <v>755580</v>
       </c>
       <c r="R16" t="n">
-        <v>7325540</v>
+        <v>7325530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676875</v>
+        <v>118676885</v>
       </c>
       <c r="B17" t="n">
         <v>79565</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755740</v>
+        <v>755570</v>
       </c>
       <c r="R17" t="n">
-        <v>7325550</v>
+        <v>7325450</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676884</v>
+        <v>118676888</v>
       </c>
       <c r="B18" t="n">
         <v>79565</v>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755578</v>
+        <v>755547</v>
       </c>
       <c r="R18" t="n">
-        <v>7325440</v>
+        <v>7325460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118676888</v>
+        <v>118676891</v>
       </c>
       <c r="B19" t="n">
         <v>79565</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755547</v>
+        <v>755576</v>
       </c>
       <c r="R19" t="n">
-        <v>7325460</v>
+        <v>7325600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118676882</v>
+        <v>118676883</v>
       </c>
       <c r="B20" t="n">
         <v>79565</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755529</v>
+        <v>755566</v>
       </c>
       <c r="R20" t="n">
-        <v>7325440</v>
+        <v>7325430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118676881</v>
+        <v>118676887</v>
       </c>
       <c r="B21" t="n">
         <v>79565</v>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>755600</v>
+        <v>755550</v>
       </c>
       <c r="R21" t="n">
-        <v>7325380</v>
+        <v>7325440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118676879</v>
+        <v>118676880</v>
       </c>
       <c r="B22" t="n">
         <v>79565</v>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>755623</v>
+        <v>755615</v>
       </c>
       <c r="R22" t="n">
-        <v>7325370</v>
+        <v>7325360</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118676885</v>
+        <v>118676874</v>
       </c>
       <c r="B23" t="n">
         <v>79565</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>755570</v>
+        <v>755750</v>
       </c>
       <c r="R23" t="n">
-        <v>7325450</v>
+        <v>7325540</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118676912</v>
+        <v>118676917</v>
       </c>
       <c r="B26" t="n">
         <v>79565</v>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>756053</v>
+        <v>755893</v>
       </c>
       <c r="R26" t="n">
-        <v>7325150</v>
+        <v>7325080</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118676911</v>
+        <v>118676878</v>
       </c>
       <c r="B27" t="n">
         <v>79565</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>755823</v>
+        <v>755804</v>
       </c>
       <c r="R27" t="n">
-        <v>7325260</v>
+        <v>7325480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3561,7 +3561,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118676916</v>
+        <v>118676877</v>
       </c>
       <c r="B28" t="n">
         <v>79565</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>756135</v>
+        <v>755808</v>
       </c>
       <c r="R28" t="n">
-        <v>7324870</v>
+        <v>7325520</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3672,7 +3672,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118676877</v>
+        <v>118676911</v>
       </c>
       <c r="B29" t="n">
         <v>79565</v>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>755808</v>
+        <v>755823</v>
       </c>
       <c r="R29" t="n">
-        <v>7325520</v>
+        <v>7325260</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3783,7 +3783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118676917</v>
+        <v>118676916</v>
       </c>
       <c r="B30" t="n">
         <v>79565</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>755893</v>
+        <v>756135</v>
       </c>
       <c r="R30" t="n">
-        <v>7325080</v>
+        <v>7324870</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118676878</v>
+        <v>118676876</v>
       </c>
       <c r="B31" t="n">
         <v>79565</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>755804</v>
+        <v>755826</v>
       </c>
       <c r="R31" t="n">
-        <v>7325480</v>
+        <v>7325540</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118676914</v>
+        <v>118676915</v>
       </c>
       <c r="B32" t="n">
         <v>79565</v>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>756137</v>
+        <v>756155</v>
       </c>
       <c r="R32" t="n">
-        <v>7324930</v>
+        <v>7324910</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118676876</v>
+        <v>118676914</v>
       </c>
       <c r="B34" t="n">
         <v>79565</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>755826</v>
+        <v>756137</v>
       </c>
       <c r="R34" t="n">
-        <v>7325540</v>
+        <v>7324930</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118676915</v>
+        <v>118676912</v>
       </c>
       <c r="B35" t="n">
         <v>79565</v>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>756155</v>
+        <v>756053</v>
       </c>
       <c r="R35" t="n">
-        <v>7324910</v>
+        <v>7325150</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676881</v>
+        <v>118676882</v>
       </c>
       <c r="B7" t="n">
         <v>79565</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755600</v>
+        <v>755529</v>
       </c>
       <c r="R7" t="n">
-        <v>7325380</v>
+        <v>7325440</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676886</v>
+        <v>118676874</v>
       </c>
       <c r="B8" t="n">
         <v>79565</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755563</v>
+        <v>755750</v>
       </c>
       <c r="R8" t="n">
-        <v>7325460</v>
+        <v>7325540</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118676890</v>
+        <v>118676892</v>
       </c>
       <c r="B9" t="n">
         <v>79565</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755578</v>
+        <v>755563</v>
       </c>
       <c r="R9" t="n">
-        <v>7325600</v>
+        <v>7325580</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118676892</v>
+        <v>118676891</v>
       </c>
       <c r="B10" t="n">
         <v>79565</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755563</v>
+        <v>755576</v>
       </c>
       <c r="R10" t="n">
-        <v>7325580</v>
+        <v>7325600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118676879</v>
+        <v>118676890</v>
       </c>
       <c r="B11" t="n">
         <v>79565</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755623</v>
+        <v>755578</v>
       </c>
       <c r="R11" t="n">
-        <v>7325370</v>
+        <v>7325600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118676889</v>
+        <v>118676893</v>
       </c>
       <c r="B12" t="n">
         <v>79565</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755541</v>
+        <v>755580</v>
       </c>
       <c r="R12" t="n">
-        <v>7325470</v>
+        <v>7325530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118676882</v>
+        <v>118676889</v>
       </c>
       <c r="B13" t="n">
         <v>79565</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755529</v>
+        <v>755541</v>
       </c>
       <c r="R13" t="n">
-        <v>7325440</v>
+        <v>7325470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118676884</v>
+        <v>118676887</v>
       </c>
       <c r="B14" t="n">
         <v>79565</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755578</v>
+        <v>755550</v>
       </c>
       <c r="R14" t="n">
         <v>7325440</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118676893</v>
+        <v>118676879</v>
       </c>
       <c r="B16" t="n">
         <v>79565</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755580</v>
+        <v>755623</v>
       </c>
       <c r="R16" t="n">
-        <v>7325530</v>
+        <v>7325370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676885</v>
+        <v>118676881</v>
       </c>
       <c r="B17" t="n">
         <v>79565</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755570</v>
+        <v>755600</v>
       </c>
       <c r="R17" t="n">
-        <v>7325450</v>
+        <v>7325380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676888</v>
+        <v>118676880</v>
       </c>
       <c r="B18" t="n">
         <v>79565</v>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755547</v>
+        <v>755615</v>
       </c>
       <c r="R18" t="n">
-        <v>7325460</v>
+        <v>7325360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118676891</v>
+        <v>118676885</v>
       </c>
       <c r="B19" t="n">
         <v>79565</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755576</v>
+        <v>755570</v>
       </c>
       <c r="R19" t="n">
-        <v>7325600</v>
+        <v>7325450</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118676883</v>
+        <v>118676886</v>
       </c>
       <c r="B20" t="n">
         <v>79565</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755566</v>
+        <v>755563</v>
       </c>
       <c r="R20" t="n">
-        <v>7325430</v>
+        <v>7325460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118676887</v>
+        <v>118676884</v>
       </c>
       <c r="B21" t="n">
         <v>79565</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>755550</v>
+        <v>755578</v>
       </c>
       <c r="R21" t="n">
         <v>7325440</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118676880</v>
+        <v>118676888</v>
       </c>
       <c r="B22" t="n">
         <v>79565</v>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>755615</v>
+        <v>755547</v>
       </c>
       <c r="R22" t="n">
-        <v>7325360</v>
+        <v>7325460</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118676874</v>
+        <v>118676883</v>
       </c>
       <c r="B23" t="n">
         <v>79565</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>755750</v>
+        <v>755566</v>
       </c>
       <c r="R23" t="n">
-        <v>7325540</v>
+        <v>7325430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118676917</v>
+        <v>118676878</v>
       </c>
       <c r="B26" t="n">
         <v>79565</v>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>755893</v>
+        <v>755804</v>
       </c>
       <c r="R26" t="n">
-        <v>7325080</v>
+        <v>7325480</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3450,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118676878</v>
+        <v>118676913</v>
       </c>
       <c r="B27" t="n">
         <v>79565</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>755804</v>
+        <v>756161</v>
       </c>
       <c r="R27" t="n">
-        <v>7325480</v>
+        <v>7324950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3561,7 +3561,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118676877</v>
+        <v>118676912</v>
       </c>
       <c r="B28" t="n">
         <v>79565</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>755808</v>
+        <v>756053</v>
       </c>
       <c r="R28" t="n">
-        <v>7325520</v>
+        <v>7325150</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,12 +3635,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3672,7 +3672,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118676911</v>
+        <v>118676876</v>
       </c>
       <c r="B29" t="n">
         <v>79565</v>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>755823</v>
+        <v>755826</v>
       </c>
       <c r="R29" t="n">
-        <v>7325260</v>
+        <v>7325540</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3783,7 +3783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118676916</v>
+        <v>118676915</v>
       </c>
       <c r="B30" t="n">
         <v>79565</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>756135</v>
+        <v>756155</v>
       </c>
       <c r="R30" t="n">
-        <v>7324870</v>
+        <v>7324910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118676876</v>
+        <v>118676917</v>
       </c>
       <c r="B31" t="n">
         <v>79565</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>755826</v>
+        <v>755893</v>
       </c>
       <c r="R31" t="n">
-        <v>7325540</v>
+        <v>7325080</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4005,7 +4005,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118676915</v>
+        <v>118676911</v>
       </c>
       <c r="B32" t="n">
         <v>79565</v>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>756155</v>
+        <v>755823</v>
       </c>
       <c r="R32" t="n">
-        <v>7324910</v>
+        <v>7325260</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118676913</v>
+        <v>118676916</v>
       </c>
       <c r="B33" t="n">
         <v>79565</v>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>756161</v>
+        <v>756135</v>
       </c>
       <c r="R33" t="n">
-        <v>7324950</v>
+        <v>7324870</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118676912</v>
+        <v>118676877</v>
       </c>
       <c r="B35" t="n">
         <v>79565</v>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>756053</v>
+        <v>755808</v>
       </c>
       <c r="R35" t="n">
-        <v>7325150</v>
+        <v>7325520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676882</v>
+        <v>118676887</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755529</v>
+        <v>755550</v>
       </c>
       <c r="R7" t="n">
         <v>7325440</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676874</v>
+        <v>118676875</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755750</v>
+        <v>755740</v>
       </c>
       <c r="R8" t="n">
-        <v>7325540</v>
+        <v>7325550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
         <v>118676892</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118676891</v>
+        <v>118676888</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755576</v>
+        <v>755547</v>
       </c>
       <c r="R10" t="n">
-        <v>7325600</v>
+        <v>7325460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
         <v>118676890</v>
       </c>
       <c r="B11" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118676893</v>
+        <v>118676884</v>
       </c>
       <c r="B12" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755580</v>
+        <v>755578</v>
       </c>
       <c r="R12" t="n">
-        <v>7325530</v>
+        <v>7325440</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>118676889</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118676887</v>
+        <v>118676874</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755550</v>
+        <v>755750</v>
       </c>
       <c r="R14" t="n">
-        <v>7325440</v>
+        <v>7325540</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118676875</v>
+        <v>118676886</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755740</v>
+        <v>755563</v>
       </c>
       <c r="R15" t="n">
-        <v>7325550</v>
+        <v>7325460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
         <v>118676879</v>
       </c>
       <c r="B16" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676881</v>
+        <v>118676883</v>
       </c>
       <c r="B17" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755600</v>
+        <v>755566</v>
       </c>
       <c r="R17" t="n">
-        <v>7325380</v>
+        <v>7325430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676880</v>
+        <v>118676885</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755615</v>
+        <v>755570</v>
       </c>
       <c r="R18" t="n">
-        <v>7325360</v>
+        <v>7325450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118676885</v>
+        <v>118676893</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755570</v>
+        <v>755580</v>
       </c>
       <c r="R19" t="n">
-        <v>7325450</v>
+        <v>7325530</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118676886</v>
+        <v>118676881</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755563</v>
+        <v>755600</v>
       </c>
       <c r="R20" t="n">
-        <v>7325460</v>
+        <v>7325380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118676884</v>
+        <v>118676880</v>
       </c>
       <c r="B21" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>755578</v>
+        <v>755615</v>
       </c>
       <c r="R21" t="n">
-        <v>7325440</v>
+        <v>7325360</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118676888</v>
+        <v>118676891</v>
       </c>
       <c r="B22" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>755547</v>
+        <v>755576</v>
       </c>
       <c r="R22" t="n">
-        <v>7325460</v>
+        <v>7325600</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118676883</v>
+        <v>118676882</v>
       </c>
       <c r="B23" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>755566</v>
+        <v>755529</v>
       </c>
       <c r="R23" t="n">
-        <v>7325430</v>
+        <v>7325440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118676878</v>
+        <v>118676913</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>755804</v>
+        <v>756161</v>
       </c>
       <c r="R26" t="n">
-        <v>7325480</v>
+        <v>7324950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3450,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118676913</v>
+        <v>118676878</v>
       </c>
       <c r="B27" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>756161</v>
+        <v>755804</v>
       </c>
       <c r="R27" t="n">
-        <v>7324950</v>
+        <v>7325480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3561,10 +3561,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118676912</v>
+        <v>118676911</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>756053</v>
+        <v>755823</v>
       </c>
       <c r="R28" t="n">
-        <v>7325150</v>
+        <v>7325260</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118676876</v>
+        <v>118676916</v>
       </c>
       <c r="B29" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>755826</v>
+        <v>756135</v>
       </c>
       <c r="R29" t="n">
-        <v>7325540</v>
+        <v>7324870</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118676915</v>
+        <v>118676917</v>
       </c>
       <c r="B30" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>756155</v>
+        <v>755893</v>
       </c>
       <c r="R30" t="n">
-        <v>7324910</v>
+        <v>7325080</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118676917</v>
+        <v>118676877</v>
       </c>
       <c r="B31" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>755893</v>
+        <v>755808</v>
       </c>
       <c r="R31" t="n">
-        <v>7325080</v>
+        <v>7325520</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4005,10 +4005,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118676911</v>
+        <v>118676912</v>
       </c>
       <c r="B32" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>755823</v>
+        <v>756053</v>
       </c>
       <c r="R32" t="n">
-        <v>7325260</v>
+        <v>7325150</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4116,10 +4116,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118676916</v>
+        <v>118676915</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>756135</v>
+        <v>756155</v>
       </c>
       <c r="R33" t="n">
-        <v>7324870</v>
+        <v>7324910</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,10 +4227,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118676914</v>
+        <v>118676876</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>756137</v>
+        <v>755826</v>
       </c>
       <c r="R34" t="n">
-        <v>7324930</v>
+        <v>7325540</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4338,10 +4338,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118676877</v>
+        <v>118676914</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>755808</v>
+        <v>756137</v>
       </c>
       <c r="R35" t="n">
-        <v>7325520</v>
+        <v>7324930</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118676890</v>
+        <v>118676884</v>
       </c>
       <c r="B11" t="n">
         <v>79572</v>
@@ -1721,7 +1721,7 @@
         <v>755578</v>
       </c>
       <c r="R11" t="n">
-        <v>7325600</v>
+        <v>7325440</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118676884</v>
+        <v>118676890</v>
       </c>
       <c r="B12" t="n">
         <v>79572</v>
@@ -1832,7 +1832,7 @@
         <v>755578</v>
       </c>
       <c r="R12" t="n">
-        <v>7325440</v>
+        <v>7325600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 26595-2024 artfynd.xlsx
+++ b/artfynd/A 26595-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676887</v>
+        <v>118676882</v>
       </c>
       <c r="B7" t="n">
         <v>79572</v>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755550</v>
+        <v>755529</v>
       </c>
       <c r="R7" t="n">
         <v>7325440</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676875</v>
+        <v>118676886</v>
       </c>
       <c r="B8" t="n">
         <v>79572</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755740</v>
+        <v>755563</v>
       </c>
       <c r="R8" t="n">
-        <v>7325550</v>
+        <v>7325460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118676892</v>
+        <v>118676874</v>
       </c>
       <c r="B9" t="n">
         <v>79572</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755563</v>
+        <v>755750</v>
       </c>
       <c r="R9" t="n">
-        <v>7325580</v>
+        <v>7325540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118676888</v>
+        <v>118676885</v>
       </c>
       <c r="B10" t="n">
         <v>79572</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>755547</v>
+        <v>755570</v>
       </c>
       <c r="R10" t="n">
-        <v>7325460</v>
+        <v>7325450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118676884</v>
+        <v>118676893</v>
       </c>
       <c r="B11" t="n">
         <v>79572</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755578</v>
+        <v>755580</v>
       </c>
       <c r="R11" t="n">
-        <v>7325440</v>
+        <v>7325530</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118676890</v>
+        <v>118676879</v>
       </c>
       <c r="B12" t="n">
         <v>79572</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755578</v>
+        <v>755623</v>
       </c>
       <c r="R12" t="n">
-        <v>7325600</v>
+        <v>7325370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118676889</v>
+        <v>118676880</v>
       </c>
       <c r="B13" t="n">
         <v>79572</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>755541</v>
+        <v>755615</v>
       </c>
       <c r="R13" t="n">
-        <v>7325470</v>
+        <v>7325360</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118676874</v>
+        <v>118676889</v>
       </c>
       <c r="B14" t="n">
         <v>79572</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755750</v>
+        <v>755541</v>
       </c>
       <c r="R14" t="n">
-        <v>7325540</v>
+        <v>7325470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118676886</v>
+        <v>118676891</v>
       </c>
       <c r="B15" t="n">
         <v>79572</v>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755563</v>
+        <v>755576</v>
       </c>
       <c r="R15" t="n">
-        <v>7325460</v>
+        <v>7325600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118676879</v>
+        <v>118676875</v>
       </c>
       <c r="B16" t="n">
         <v>79572</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>755623</v>
+        <v>755740</v>
       </c>
       <c r="R16" t="n">
-        <v>7325370</v>
+        <v>7325550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118676883</v>
+        <v>118676890</v>
       </c>
       <c r="B17" t="n">
         <v>79572</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>755566</v>
+        <v>755578</v>
       </c>
       <c r="R17" t="n">
-        <v>7325430</v>
+        <v>7325600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118676885</v>
+        <v>118676887</v>
       </c>
       <c r="B18" t="n">
         <v>79572</v>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755570</v>
+        <v>755550</v>
       </c>
       <c r="R18" t="n">
-        <v>7325450</v>
+        <v>7325440</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118676893</v>
+        <v>118676883</v>
       </c>
       <c r="B19" t="n">
         <v>79572</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755580</v>
+        <v>755566</v>
       </c>
       <c r="R19" t="n">
-        <v>7325530</v>
+        <v>7325430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118676881</v>
+        <v>118676888</v>
       </c>
       <c r="B20" t="n">
         <v>79572</v>
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755600</v>
+        <v>755547</v>
       </c>
       <c r="R20" t="n">
-        <v>7325380</v>
+        <v>7325460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118676880</v>
+        <v>118676884</v>
       </c>
       <c r="B21" t="n">
         <v>79572</v>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>755615</v>
+        <v>755578</v>
       </c>
       <c r="R21" t="n">
-        <v>7325360</v>
+        <v>7325440</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118676891</v>
+        <v>118676881</v>
       </c>
       <c r="B22" t="n">
         <v>79572</v>
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>755576</v>
+        <v>755600</v>
       </c>
       <c r="R22" t="n">
-        <v>7325600</v>
+        <v>7325380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118676882</v>
+        <v>118676892</v>
       </c>
       <c r="B23" t="n">
         <v>79572</v>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>755529</v>
+        <v>755563</v>
       </c>
       <c r="R23" t="n">
-        <v>7325440</v>
+        <v>7325580</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118676913</v>
+        <v>118676914</v>
       </c>
       <c r="B26" t="n">
         <v>79572</v>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>756161</v>
+        <v>756137</v>
       </c>
       <c r="R26" t="n">
-        <v>7324950</v>
+        <v>7324930</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118676878</v>
+        <v>118676911</v>
       </c>
       <c r="B27" t="n">
         <v>79572</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>755804</v>
+        <v>755823</v>
       </c>
       <c r="R27" t="n">
-        <v>7325480</v>
+        <v>7325260</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3561,7 +3561,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118676911</v>
+        <v>118676913</v>
       </c>
       <c r="B28" t="n">
         <v>79572</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>755823</v>
+        <v>756161</v>
       </c>
       <c r="R28" t="n">
-        <v>7325260</v>
+        <v>7324950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118676916</v>
+        <v>118676878</v>
       </c>
       <c r="B29" t="n">
         <v>79572</v>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>756135</v>
+        <v>755804</v>
       </c>
       <c r="R29" t="n">
-        <v>7324870</v>
+        <v>7325480</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3783,7 +3783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118676917</v>
+        <v>118676876</v>
       </c>
       <c r="B30" t="n">
         <v>79572</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>755893</v>
+        <v>755826</v>
       </c>
       <c r="R30" t="n">
-        <v>7325080</v>
+        <v>7325540</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3894,7 +3894,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118676877</v>
+        <v>118676912</v>
       </c>
       <c r="B31" t="n">
         <v>79572</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>755808</v>
+        <v>756053</v>
       </c>
       <c r="R31" t="n">
-        <v>7325520</v>
+        <v>7325150</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4005,7 +4005,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118676912</v>
+        <v>118676877</v>
       </c>
       <c r="B32" t="n">
         <v>79572</v>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>756053</v>
+        <v>755808</v>
       </c>
       <c r="R32" t="n">
-        <v>7325150</v>
+        <v>7325520</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4079,12 +4079,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4116,7 +4116,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118676915</v>
+        <v>118676916</v>
       </c>
       <c r="B33" t="n">
         <v>79572</v>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>756155</v>
+        <v>756135</v>
       </c>
       <c r="R33" t="n">
-        <v>7324910</v>
+        <v>7324870</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118676876</v>
+        <v>118676915</v>
       </c>
       <c r="B34" t="n">
         <v>79572</v>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>755826</v>
+        <v>756155</v>
       </c>
       <c r="R34" t="n">
-        <v>7325540</v>
+        <v>7324910</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118676914</v>
+        <v>118676917</v>
       </c>
       <c r="B35" t="n">
         <v>79572</v>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>756137</v>
+        <v>755893</v>
       </c>
       <c r="R35" t="n">
-        <v>7324930</v>
+        <v>7325080</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
